--- a/04_26.xlsx
+++ b/04_26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3BC274C-6552-ED4A-A5FB-DE346734BD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A078BBE-D8ED-484B-B1A3-60EED3221DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="780" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="149">
   <si>
     <t>Event</t>
   </si>
@@ -3469,8 +3491,8 @@
       <c r="AF1" s="2"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>142</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3564,8 +3586,8 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>89</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3590,8 +3612,8 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>90</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -3604,13 +3626,13 @@
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>91</v>
+      <c r="A5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>92</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3638,8 +3660,8 @@
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>143</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3733,8 +3755,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>144</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3828,13 +3850,13 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>93</v>
+      <c r="A9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>94</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -3844,13 +3866,13 @@
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>95</v>
+      <c r="A11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>96</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -3896,18 +3918,18 @@
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>97</v>
+      <c r="A13">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>98</v>
+      <c r="A14">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>99</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -3941,13 +3963,13 @@
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>100</v>
+      <c r="A16">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>101</v>
+      <c r="A17">
+        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -3969,13 +3991,13 @@
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>102</v>
+      <c r="A18">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>103</v>
+      <c r="A19">
+        <v>18</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4039,13 +4061,13 @@
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>104</v>
+      <c r="A20">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>105</v>
+      <c r="A21">
+        <v>20</v>
       </c>
       <c r="T21">
         <v>1</v>
@@ -4058,8 +4080,8 @@
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>145</v>
+      <c r="A22">
+        <v>21</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -4153,18 +4175,18 @@
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>106</v>
+      <c r="A23">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>146</v>
+      <c r="A24">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>107</v>
+      <c r="A25">
+        <v>24</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -4204,8 +4226,8 @@
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>147</v>
+      <c r="A26">
+        <v>25</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -4299,13 +4321,13 @@
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>108</v>
+      <c r="A27">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>109</v>
+      <c r="A28">
+        <v>27</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4327,8 +4349,8 @@
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>110</v>
+      <c r="A29">
+        <v>28</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4350,8 +4372,8 @@
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>111</v>
+      <c r="A30">
+        <v>29</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -4376,28 +4398,28 @@
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>112</v>
+      <c r="A31">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>113</v>
+      <c r="A32">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>114</v>
+      <c r="A33">
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>115</v>
+      <c r="A34">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>148</v>
+      <c r="A35">
+        <v>34</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -4491,36 +4513,36 @@
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>116</v>
+      <c r="A36">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>117</v>
+      <c r="A37">
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>118</v>
+      <c r="A38">
+        <v>37</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>119</v>
+      <c r="A39">
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>120</v>
+      <c r="A40">
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>121</v>
+      <c r="A41">
+        <v>40</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -4554,8 +4576,8 @@
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>122</v>
+      <c r="A42">
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4566,14 +4588,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AQ49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4718,8 +4740,36 @@
         <f>Employees!B35</f>
         <v>Vero</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AK1" s="1" t="str">
+        <f>Employees!B36</f>
+        <v xml:space="preserve">Védís </v>
+      </c>
+      <c r="AL1" s="1" t="str" cm="1">
+        <f t="array" ref="AL1">TRANSPOSE(Employees!B37)</f>
+        <v xml:space="preserve">Unnar </v>
+      </c>
+      <c r="AM1" s="1" t="str">
+        <f>Employees!B38</f>
+        <v>Ömmi</v>
+      </c>
+      <c r="AN1" s="1" t="str">
+        <f>Employees!B39</f>
+        <v xml:space="preserve">Arnar </v>
+      </c>
+      <c r="AO1" s="1" t="str">
+        <f>Employees!B40</f>
+        <v xml:space="preserve">Róbert </v>
+      </c>
+      <c r="AP1" s="1" t="str">
+        <f>Employees!B41</f>
+        <v xml:space="preserve">Jara </v>
+      </c>
+      <c r="AQ1" s="1" t="str">
+        <f>Employees!B42</f>
+        <v xml:space="preserve">Þórey </v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>Múlinn</v>
@@ -4729,7 +4779,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>RF</v>
@@ -4739,7 +4789,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>VH</v>
@@ -4749,7 +4799,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RF</v>
@@ -4759,7 +4809,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>VH</v>
@@ -4769,7 +4819,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>VH</v>
@@ -4779,7 +4829,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>Múlinn</v>
@@ -4789,7 +4839,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>Sinfó</v>
@@ -4799,7 +4849,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4809,7 +4859,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4819,7 +4869,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>PL</v>
@@ -4829,7 +4879,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>Fam</v>
@@ -4839,7 +4889,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>Sinfó</v>
@@ -4849,7 +4899,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>Upprás</v>
@@ -4859,7 +4909,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>Múlinn</v>
